--- a/09_meetings/Yokohama_2026/ISZE_GPS_Extended_Target_FY27_V3.3.xlsx
+++ b/09_meetings/Yokohama_2026/ISZE_GPS_Extended_Target_FY27_V3.3.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="537">
   <si>
     <t xml:space="preserve">ISZE — FY2027 GPS Extended Target</t>
   </si>
@@ -999,6 +999,12 @@
     <t xml:space="preserve">Stretch total FY27 = sum over the 16 tabs + ITUK + UTI</t>
   </si>
   <si>
+    <t xml:space="preserve">ITUK max spend: Dashboard = Japanese view (MH data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTI max spend: Dashboard = Japanese view (MH data)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gap row FY31 = target + outside - BP</t>
   </si>
   <si>
@@ -1161,7 +1167,7 @@
     <t xml:space="preserve">INFO</t>
   </si>
   <si>
-    <t xml:space="preserve">Known, not an error: ITUK and UTI potential differ between Dashboard (V4 basis, 13.05M / 8.83M) and Dashboard (2) (fleet 2026 by N35/N75/F, 12.54M / 8.49M). Both are as presented; targets agree.</t>
+    <t xml:space="preserve">ITUK and UTI max spend use Masumi-san's data on both dashboards (12.54M / 8.49M, 2026 vehicles, +5%). Targets and stretch stay as presented in July (V4).</t>
   </si>
   <si>
     <t xml:space="preserve">Not verifiable inside the repo: KPI sales-to-dealer (Dashboard col Q, from KPI Master File June 2026), ITUK/UTI V4 figures, waterfall bars. They are carried from V3.2 unchanged.</t>
@@ -1207,6 +1213,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max spend on MH data (2026 vehicles, +5%); target as presented</t>
   </si>
   <si>
     <t xml:space="preserve">Skipped</t>
@@ -4020,11 +4029,11 @@
       </c>
       <c r="D6" s="25" t="n">
         <f aca="false">Dashboard!D5</f>
-        <v>13051952.5629</v>
+        <v>12535797.12</v>
       </c>
       <c r="E6" s="26" t="n">
         <f aca="false">Dashboard!E5</f>
-        <v>0.534339212373786</v>
+        <v>0.556340373542995</v>
       </c>
       <c r="F6" s="24" t="n">
         <f aca="false">Dashboard!F5</f>
@@ -4757,11 +4766,11 @@
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">Dashboard!D6</f>
-        <v>8834692</v>
+        <v>8485128.96</v>
       </c>
       <c r="E10" s="26" t="n">
         <f aca="false">Dashboard!E6</f>
-        <v>0.350675892674017</v>
+        <v>0.365122736284258</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">Dashboard!F6</f>
@@ -11873,11 +11882,11 @@
       </c>
       <c r="D44" s="28" t="n">
         <f aca="false">SUM(D6:D41)</f>
-        <v>61019133.4129</v>
+        <v>60153414.93</v>
       </c>
       <c r="E44" s="42" t="n">
         <f aca="false">C44/D44</f>
-        <v>0.544458108429585</v>
+        <v>0.552293863858944</v>
       </c>
       <c r="F44" s="24"/>
       <c r="G44" s="28" t="n">
@@ -12279,32 +12288,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -12312,30 +12321,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12366,7 +12375,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -12399,39 +12408,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -12465,40 +12474,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -12531,7 +12540,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>365817.37</v>
@@ -12546,7 +12555,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -12563,7 +12572,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -12578,7 +12587,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -12595,7 +12604,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -12612,7 +12621,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -12629,33 +12638,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>934209</v>
@@ -12664,12 +12673,12 @@
         <v>871455</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -12679,7 +12688,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -12688,7 +12697,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -12697,17 +12706,17 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -12737,32 +12746,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -12770,30 +12779,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12824,7 +12833,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -12857,39 +12866,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -12923,40 +12932,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -12989,7 +12998,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>266204.48</v>
@@ -13004,7 +13013,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -13021,7 +13030,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -13036,7 +13045,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -13053,7 +13062,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -13070,7 +13079,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -13087,33 +13096,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>576758</v>
@@ -13122,12 +13131,12 @@
         <v>350854</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -13137,7 +13146,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -13146,7 +13155,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -13155,22 +13164,22 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="80" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -13200,32 +13209,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -13233,30 +13242,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13287,7 +13296,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -13320,39 +13329,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -13386,40 +13395,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -13452,7 +13461,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>151600.22</v>
@@ -13467,7 +13476,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -13484,7 +13493,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -13499,7 +13508,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -13516,7 +13525,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -13533,7 +13542,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -13550,33 +13559,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>382258</v>
@@ -13585,12 +13594,12 @@
         <v>394596.629253138</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -13600,7 +13609,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -13609,7 +13618,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -13618,22 +13627,22 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="80" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -13663,32 +13672,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -13696,30 +13705,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13750,7 +13759,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -13783,39 +13792,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -13849,40 +13858,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -13915,7 +13924,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>122628.72</v>
@@ -13930,7 +13939,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -13947,7 +13956,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -13962,7 +13971,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -13979,7 +13988,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -13996,7 +14005,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -14013,33 +14022,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>356680.16</v>
@@ -14048,12 +14057,12 @@
         <v>572863.67</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -14063,7 +14072,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -14072,7 +14081,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -14081,17 +14090,17 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -14121,32 +14130,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -14154,30 +14163,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14208,7 +14217,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -14241,39 +14250,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -14307,40 +14316,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -14373,7 +14382,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>73673.52</v>
@@ -14388,7 +14397,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -14405,7 +14414,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -14420,7 +14429,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -14437,7 +14446,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -14454,7 +14463,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -14471,33 +14480,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>209944</v>
@@ -14506,12 +14515,12 @@
         <v>195849</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -14521,7 +14530,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -14530,7 +14539,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -14539,17 +14548,17 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14582,32 +14591,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -14615,35 +14624,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>719</v>
@@ -14669,7 +14678,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>36</v>
@@ -14695,7 +14704,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>0</v>
@@ -14747,7 +14756,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -14780,35 +14789,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -14837,7 +14846,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -14866,7 +14875,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -14895,7 +14904,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -14924,40 +14933,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -14990,7 +14999,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>2589331.92</v>
@@ -15005,7 +15014,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -15022,7 +15031,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -15037,7 +15046,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -15054,7 +15063,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -15071,7 +15080,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -15088,45 +15097,45 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>4475521</v>
       </c>
       <c r="D36" s="123"/>
       <c r="F36" s="131" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -15136,7 +15145,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -15145,7 +15154,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="str">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -15154,22 +15163,22 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="80" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -15199,32 +15208,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -15232,35 +15241,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>123</v>
@@ -15286,7 +15295,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -15312,7 +15321,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>0</v>
@@ -15364,7 +15373,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -15397,35 +15406,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -15454,7 +15463,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -15483,7 +15492,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -15512,7 +15521,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -15541,40 +15550,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -15607,7 +15616,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>2229128.61</v>
@@ -15622,7 +15631,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -15639,7 +15648,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -15654,7 +15663,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -15671,7 +15680,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -15688,7 +15697,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -15705,33 +15714,33 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>4056302</v>
@@ -15740,12 +15749,12 @@
         <v>6834272</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -15755,7 +15764,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -15764,7 +15773,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="n">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -15773,22 +15782,22 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="80" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -15818,32 +15827,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -15851,35 +15860,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>2239</v>
@@ -15905,7 +15914,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -15931,7 +15940,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>254</v>
@@ -15983,7 +15992,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -16016,35 +16025,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -16073,7 +16082,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -16102,7 +16111,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -16131,7 +16140,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -16160,40 +16169,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -16226,7 +16235,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>1544440.63</v>
@@ -16241,7 +16250,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -16258,7 +16267,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -16273,7 +16282,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -16290,7 +16299,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -16307,7 +16316,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -16324,33 +16333,33 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>2229187</v>
@@ -16359,12 +16368,12 @@
         <v>4047903</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -16374,7 +16383,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -16383,7 +16392,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="n">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -16392,17 +16401,17 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -16432,32 +16441,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -16465,35 +16474,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>749</v>
@@ -16519,7 +16528,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -16545,7 +16554,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>67</v>
@@ -16597,7 +16606,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -16630,35 +16639,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -16687,7 +16696,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -16716,7 +16725,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -16745,7 +16754,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -16774,40 +16783,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -16840,7 +16849,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>1222521.53</v>
@@ -16855,7 +16864,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -16872,7 +16881,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -16887,7 +16896,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -16904,7 +16913,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -16921,7 +16930,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -16938,33 +16947,33 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>2687539</v>
@@ -16973,12 +16982,12 @@
         <v>2833637</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -16988,7 +16997,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -16997,7 +17006,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="n">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -17006,22 +17015,22 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="80" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -17051,32 +17060,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -17084,35 +17093,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>43</v>
@@ -17138,7 +17147,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -17164,7 +17173,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>0</v>
@@ -17216,7 +17225,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -17249,35 +17258,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -17306,7 +17315,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -17335,7 +17344,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -17364,7 +17373,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -17393,40 +17402,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -17459,7 +17468,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>460697.42</v>
@@ -17474,7 +17483,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -17491,7 +17500,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -17506,7 +17515,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -17523,7 +17532,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -17540,7 +17549,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -17557,45 +17566,45 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>515115</v>
       </c>
       <c r="D36" s="123"/>
       <c r="F36" s="131" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -17605,7 +17614,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -17614,7 +17623,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="str">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -17623,22 +17632,22 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="80" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -18053,32 +18062,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -18086,35 +18095,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>213</v>
@@ -18140,7 +18149,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -18166,7 +18175,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>0</v>
@@ -18218,7 +18227,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -18251,35 +18260,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -18308,7 +18317,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -18337,7 +18346,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -18366,7 +18375,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -18395,40 +18404,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -18461,7 +18470,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>395930.56</v>
@@ -18476,7 +18485,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -18493,7 +18502,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -18508,7 +18517,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -18525,7 +18534,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -18542,7 +18551,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -18559,43 +18568,43 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123"/>
       <c r="D36" s="123"/>
       <c r="F36" s="131" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -18605,7 +18614,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -18614,7 +18623,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="str">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -18623,17 +18632,17 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -18663,32 +18672,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -18696,35 +18705,35 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C9" s="118" t="n">
         <v>261</v>
@@ -18750,7 +18759,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="118" t="n">
         <v>0</v>
@@ -18776,7 +18785,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C11" s="118" t="n">
         <v>0</v>
@@ -18828,7 +18837,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -18861,35 +18870,35 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E16" s="119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G16" s="119" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H16" s="119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C17" s="132" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -18918,7 +18927,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C18" s="132" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -18947,7 +18956,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C19" s="132" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -18976,7 +18985,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="133" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -19005,40 +19014,40 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H24" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I24" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">C9*$C$17+C10*$C$18+C11*$C$19+C12*$C$20</f>
@@ -19071,7 +19080,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26" s="123" t="n">
         <v>208360.36</v>
@@ -19086,7 +19095,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27" s="96" t="n">
         <f aca="false">C26/C25</f>
@@ -19103,7 +19112,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28" s="124" t="n">
         <v>0</v>
@@ -19118,7 +19127,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29" s="61" t="n">
         <f aca="false">C25*C28</f>
@@ -19135,7 +19144,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30" s="79" t="n">
         <f aca="false">C26+C29</f>
@@ -19152,7 +19161,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31" s="56" t="n">
         <f aca="false">C30/C25</f>
@@ -19169,33 +19178,33 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C36" s="123" t="n">
         <v>555482</v>
@@ -19204,12 +19213,12 @@
         <v>553873</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B37" s="126" t="n">
         <v>0.35</v>
@@ -19219,7 +19228,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E38" s="128" t="n">
         <f aca="false">-E29/(B37-1)</f>
@@ -19228,7 +19237,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E39" s="129" t="n">
         <f aca="false">IF(OR(D36="",D36="no KPI data"),"no KPI data",D36+E38)</f>
@@ -19237,17 +19246,17 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="80" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -19275,12 +19284,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19288,7 +19297,7 @@
         <v>952037.422457297</v>
       </c>
       <c r="S7" s="55" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19296,7 +19305,7 @@
         <v>210000</v>
       </c>
       <c r="P8" s="55" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="Q8" s="123" t="n">
         <v>-260000</v>
@@ -19307,7 +19316,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="O9" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R9" s="123" t="n">
         <v>-350000</v>
@@ -19318,7 +19327,7 @@
         <v>378908</v>
       </c>
       <c r="Q10" s="55" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="S10" s="123" t="n">
         <v>35284444.2378</v>
@@ -19329,10 +19338,10 @@
         <v>93000</v>
       </c>
       <c r="N11" s="55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="R11" s="55" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19345,13 +19354,13 @@
         <v>280000</v>
       </c>
       <c r="K13" s="55" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M13" s="55" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N13" s="55" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19362,13 +19371,13 @@
         <v>11940</v>
       </c>
       <c r="J14" s="55" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M14" s="55" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N14" s="55" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19376,13 +19385,13 @@
         <v>75000</v>
       </c>
       <c r="H15" s="55" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N15" s="55" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19390,16 +19399,16 @@
         <v>60000</v>
       </c>
       <c r="G16" s="55" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N16" s="55" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19407,16 +19416,16 @@
         <v>96664.1975427</v>
       </c>
       <c r="F17" s="55" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H17" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="N17" s="55" t="s">
         <v>287</v>
-      </c>
-      <c r="I17" s="55" t="s">
-        <v>288</v>
-      </c>
-      <c r="N17" s="55" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19424,13 +19433,13 @@
         <v>691851.847800002</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H18" s="55" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I18" s="55" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19438,45 +19447,45 @@
         <v>32944042.77</v>
       </c>
       <c r="D19" s="55" t="s">
+        <v>297</v>
+      </c>
+      <c r="H19" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="I19" s="55" t="s">
         <v>294</v>
-      </c>
-      <c r="H19" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="I19" s="55" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H20" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="I20" s="0" t="s">
         <v>296</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H21" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H22" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="S28" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -19503,7 +19512,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19511,32 +19520,32 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="67" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="67" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="67" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="67" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="67" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="67" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19544,37 +19553,37 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="98" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="67" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="67" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="67" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19582,22 +19591,22 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="67" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="67" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="67" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19605,22 +19614,22 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="81" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="81" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19628,32 +19637,32 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="81" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="81" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="81" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="81" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="81" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19661,37 +19670,37 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="81" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="81" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="81" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="81" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="81" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="81" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19699,12 +19708,12 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="81" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19712,77 +19721,77 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="81" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -19801,7 +19810,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -20020,12 +20029,12 @@
         <v>164</v>
       </c>
       <c r="C12" s="57" t="n">
-        <f aca="false">'Dashboard (2)'!BN47</f>
-        <v>1501212.37691522</v>
+        <f aca="false">Dashboard!D5</f>
+        <v>12535797.12</v>
       </c>
       <c r="D12" s="57" t="n">
-        <f aca="false">'Dashboard (2)'!BN44+'Dashboard (2)'!BN45-'Dashboard (2)'!BN46</f>
-        <v>1501212.37691522</v>
+        <f aca="false">'Dashboard (2)'!X9</f>
+        <v>12535797.12</v>
       </c>
       <c r="E12" s="57" t="n">
         <f aca="false">C12-D12</f>
@@ -20044,12 +20053,12 @@
         <v>165</v>
       </c>
       <c r="C13" s="57" t="n">
-        <f aca="false">SUMPRODUCT(--ISERROR('Dashboard (2)'!A1:BR60))</f>
-        <v>0</v>
+        <f aca="false">Dashboard!D6</f>
+        <v>8485128.96</v>
       </c>
       <c r="D13" s="57" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">'Dashboard (2)'!X10</f>
+        <v>8485128.96</v>
       </c>
       <c r="E13" s="57" t="n">
         <f aca="false">C13-D13</f>
@@ -20068,12 +20077,12 @@
         <v>166</v>
       </c>
       <c r="C14" s="57" t="n">
-        <f aca="false">SUMPRODUCT(--ISERROR(Dashboard!A1:W40))</f>
-        <v>0</v>
+        <f aca="false">'Dashboard (2)'!BN47</f>
+        <v>1501212.37691522</v>
       </c>
       <c r="D14" s="57" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">'Dashboard (2)'!BN44+'Dashboard (2)'!BN45-'Dashboard (2)'!BN46</f>
+        <v>1501212.37691522</v>
       </c>
       <c r="E14" s="57" t="n">
         <f aca="false">C14-D14</f>
@@ -20092,12 +20101,12 @@
         <v>167</v>
       </c>
       <c r="C15" s="57" t="n">
-        <f aca="false">IUK!E24</f>
-        <v>6295804.49</v>
+        <f aca="false">SUMPRODUCT(--ISERROR('Dashboard (2)'!A1:BR60))</f>
+        <v>0</v>
       </c>
       <c r="D15" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I7,'Dashboard (2)'!Z11)</f>
-        <v>6295804.49</v>
+        <f aca="false">0</f>
+        <v>0</v>
       </c>
       <c r="E15" s="57" t="n">
         <f aca="false">C15-D15</f>
@@ -20116,12 +20125,12 @@
         <v>168</v>
       </c>
       <c r="C16" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H7&lt;=Inputs!$B$38+0.0000001,Dashboard!F7=0),1,0)</f>
-        <v>1</v>
+        <f aca="false">SUMPRODUCT(--ISERROR(Dashboard!A1:W40))</f>
+        <v>0</v>
       </c>
       <c r="D16" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">0</f>
+        <v>0</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">C16-D16</f>
@@ -20140,12 +20149,12 @@
         <v>169</v>
       </c>
       <c r="C17" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM11&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM11='Dashboard (2)'!Y11),1,0)</f>
-        <v>1</v>
+        <f aca="false">IUK!E24</f>
+        <v>6295804.49</v>
       </c>
       <c r="D17" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I7,'Dashboard (2)'!Z11)</f>
+        <v>6295804.49</v>
       </c>
       <c r="E17" s="57" t="n">
         <f aca="false">C17-D17</f>
@@ -20164,12 +20173,12 @@
         <v>170</v>
       </c>
       <c r="C18" s="57" t="n">
-        <f aca="false">UMI!E24</f>
-        <v>3062515.68</v>
+        <f aca="false">IF(OR(Dashboard!H7&lt;=Inputs!$B$38+0.0000001,Dashboard!F7=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D18" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I8,'Dashboard (2)'!Z12)</f>
-        <v>3062515.68</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">C18-D18</f>
@@ -20188,7 +20197,7 @@
         <v>171</v>
       </c>
       <c r="C19" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H8&lt;=Inputs!$B$38+0.0000001,Dashboard!F8=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM11&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM11='Dashboard (2)'!Y11),1,0)</f>
         <v>1</v>
       </c>
       <c r="D19" s="57" t="n">
@@ -20212,12 +20221,12 @@
         <v>172</v>
       </c>
       <c r="C20" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM12&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM12='Dashboard (2)'!Y12),1,0)</f>
-        <v>1</v>
+        <f aca="false">UMI!E24</f>
+        <v>3062515.68</v>
       </c>
       <c r="D20" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I8,'Dashboard (2)'!Z12)</f>
+        <v>3062515.68</v>
       </c>
       <c r="E20" s="57" t="n">
         <f aca="false">C20-D20</f>
@@ -20236,12 +20245,12 @@
         <v>173</v>
       </c>
       <c r="C21" s="57" t="n">
-        <f aca="false">NORWAY!E24</f>
-        <v>1803124.225</v>
+        <f aca="false">IF(OR(Dashboard!H8&lt;=Inputs!$B$38+0.0000001,Dashboard!F8=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D21" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I9,'Dashboard (2)'!Z13)</f>
-        <v>1803124.225</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E21" s="57" t="n">
         <f aca="false">C21-D21</f>
@@ -20260,7 +20269,7 @@
         <v>174</v>
       </c>
       <c r="C22" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H9&lt;=Inputs!$B$38+0.0000001,Dashboard!F9=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM12&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM12='Dashboard (2)'!Y12),1,0)</f>
         <v>1</v>
       </c>
       <c r="D22" s="57" t="n">
@@ -20284,12 +20293,12 @@
         <v>175</v>
       </c>
       <c r="C23" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM13&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM13='Dashboard (2)'!Y13),1,0)</f>
-        <v>1</v>
+        <f aca="false">NORWAY!E24</f>
+        <v>1803124.225</v>
       </c>
       <c r="D23" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I9,'Dashboard (2)'!Z13)</f>
+        <v>1803124.225</v>
       </c>
       <c r="E23" s="57" t="n">
         <f aca="false">C23-D23</f>
@@ -20308,12 +20317,12 @@
         <v>176</v>
       </c>
       <c r="C24" s="57" t="n">
-        <f aca="false">SWEDEN!E24</f>
-        <v>1507252.58</v>
+        <f aca="false">IF(OR(Dashboard!H9&lt;=Inputs!$B$38+0.0000001,Dashboard!F9=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D24" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I10,'Dashboard (2)'!Z14)</f>
-        <v>1507252.58</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E24" s="57" t="n">
         <f aca="false">C24-D24</f>
@@ -20332,7 +20341,7 @@
         <v>177</v>
       </c>
       <c r="C25" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H10&lt;=Inputs!$B$38+0.0000001,Dashboard!F10=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM13&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM13='Dashboard (2)'!Y13),1,0)</f>
         <v>1</v>
       </c>
       <c r="D25" s="57" t="n">
@@ -20356,12 +20365,12 @@
         <v>178</v>
       </c>
       <c r="C26" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM14&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM14='Dashboard (2)'!Y14),1,0)</f>
-        <v>1</v>
+        <f aca="false">SWEDEN!E24</f>
+        <v>1507252.58</v>
       </c>
       <c r="D26" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I10,'Dashboard (2)'!Z14)</f>
+        <v>1507252.58</v>
       </c>
       <c r="E26" s="57" t="n">
         <f aca="false">C26-D26</f>
@@ -20380,12 +20389,12 @@
         <v>179</v>
       </c>
       <c r="C27" s="57" t="n">
-        <f aca="false">HUNGARY!E24</f>
-        <v>368462.2</v>
+        <f aca="false">IF(OR(Dashboard!H10&lt;=Inputs!$B$38+0.0000001,Dashboard!F10=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D27" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I11,'Dashboard (2)'!Z15)</f>
-        <v>368462.2</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E27" s="57" t="n">
         <f aca="false">C27-D27</f>
@@ -20404,7 +20413,7 @@
         <v>180</v>
       </c>
       <c r="C28" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H11&lt;=Inputs!$B$38+0.0000001,Dashboard!F11=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM14&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM14='Dashboard (2)'!Y14),1,0)</f>
         <v>1</v>
       </c>
       <c r="D28" s="57" t="n">
@@ -20428,12 +20437,12 @@
         <v>181</v>
       </c>
       <c r="C29" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM15&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM15='Dashboard (2)'!Y15),1,0)</f>
-        <v>1</v>
+        <f aca="false">HUNGARY!E24</f>
+        <v>368462.2</v>
       </c>
       <c r="D29" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I11,'Dashboard (2)'!Z15)</f>
+        <v>368462.2</v>
       </c>
       <c r="E29" s="57" t="n">
         <f aca="false">C29-D29</f>
@@ -20452,12 +20461,12 @@
         <v>182</v>
       </c>
       <c r="C30" s="57" t="n">
-        <f aca="false">FINLAND!E24</f>
-        <v>366480.3</v>
+        <f aca="false">IF(OR(Dashboard!H11&lt;=Inputs!$B$38+0.0000001,Dashboard!F11=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D30" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I12,'Dashboard (2)'!Z16)</f>
-        <v>366480.3</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E30" s="57" t="n">
         <f aca="false">C30-D30</f>
@@ -20476,7 +20485,7 @@
         <v>183</v>
       </c>
       <c r="C31" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H12&lt;=Inputs!$B$38+0.0000001,Dashboard!F12=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM15&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM15='Dashboard (2)'!Y15),1,0)</f>
         <v>1</v>
       </c>
       <c r="D31" s="57" t="n">
@@ -20500,12 +20509,12 @@
         <v>184</v>
       </c>
       <c r="C32" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM16&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM16='Dashboard (2)'!Y16),1,0)</f>
-        <v>1</v>
+        <f aca="false">FINLAND!E24</f>
+        <v>366480.3</v>
       </c>
       <c r="D32" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I12,'Dashboard (2)'!Z16)</f>
+        <v>366480.3</v>
       </c>
       <c r="E32" s="57" t="n">
         <f aca="false">C32-D32</f>
@@ -20524,12 +20533,12 @@
         <v>185</v>
       </c>
       <c r="C33" s="57" t="n">
-        <f aca="false">ROMANIA!E24</f>
-        <v>205300.095</v>
+        <f aca="false">IF(OR(Dashboard!H12&lt;=Inputs!$B$38+0.0000001,Dashboard!F12=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D33" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I13,'Dashboard (2)'!Z17)</f>
-        <v>205300.095</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E33" s="57" t="n">
         <f aca="false">C33-D33</f>
@@ -20548,7 +20557,7 @@
         <v>186</v>
       </c>
       <c r="C34" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H13&lt;=Inputs!$B$38+0.0000001,Dashboard!F13=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM16&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM16='Dashboard (2)'!Y16),1,0)</f>
         <v>1</v>
       </c>
       <c r="D34" s="57" t="n">
@@ -20572,12 +20581,12 @@
         <v>187</v>
       </c>
       <c r="C35" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM17&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM17='Dashboard (2)'!Y17),1,0)</f>
-        <v>1</v>
+        <f aca="false">ROMANIA!E24</f>
+        <v>205300.095</v>
       </c>
       <c r="D35" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I13,'Dashboard (2)'!Z17)</f>
+        <v>205300.095</v>
       </c>
       <c r="E35" s="57" t="n">
         <f aca="false">C35-D35</f>
@@ -20596,12 +20605,12 @@
         <v>188</v>
       </c>
       <c r="C36" s="57" t="n">
-        <f aca="false">DENMARK!E24</f>
-        <v>192060.4</v>
+        <f aca="false">IF(OR(Dashboard!H13&lt;=Inputs!$B$38+0.0000001,Dashboard!F13=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D36" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I14,'Dashboard (2)'!Z18)</f>
-        <v>192060.4</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E36" s="57" t="n">
         <f aca="false">C36-D36</f>
@@ -20620,7 +20629,7 @@
         <v>189</v>
       </c>
       <c r="C37" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H14&lt;=Inputs!$B$38+0.0000001,Dashboard!F14=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM17&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM17='Dashboard (2)'!Y17),1,0)</f>
         <v>1</v>
       </c>
       <c r="D37" s="57" t="n">
@@ -20644,12 +20653,12 @@
         <v>190</v>
       </c>
       <c r="C38" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM18&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM18='Dashboard (2)'!Y18),1,0)</f>
-        <v>1</v>
+        <f aca="false">DENMARK!E24</f>
+        <v>192060.4</v>
       </c>
       <c r="D38" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I14,'Dashboard (2)'!Z18)</f>
+        <v>192060.4</v>
       </c>
       <c r="E38" s="57" t="n">
         <f aca="false">C38-D38</f>
@@ -20668,12 +20677,12 @@
         <v>191</v>
       </c>
       <c r="C39" s="57" t="n">
-        <f aca="false">ICELAND!E24</f>
-        <v>106674.275</v>
+        <f aca="false">IF(OR(Dashboard!H14&lt;=Inputs!$B$38+0.0000001,Dashboard!F14=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D39" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I15,'Dashboard (2)'!Z19)</f>
-        <v>106674.275</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E39" s="57" t="n">
         <f aca="false">C39-D39</f>
@@ -20692,7 +20701,7 @@
         <v>192</v>
       </c>
       <c r="C40" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H15&lt;=Inputs!$B$38+0.0000001,Dashboard!F15=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM18&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM18='Dashboard (2)'!Y18),1,0)</f>
         <v>1</v>
       </c>
       <c r="D40" s="57" t="n">
@@ -20716,12 +20725,12 @@
         <v>193</v>
       </c>
       <c r="C41" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM19&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM19='Dashboard (2)'!Y19),1,0)</f>
-        <v>1</v>
+        <f aca="false">ICELAND!E24</f>
+        <v>106674.275</v>
       </c>
       <c r="D41" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I15,'Dashboard (2)'!Z19)</f>
+        <v>106674.275</v>
       </c>
       <c r="E41" s="57" t="n">
         <f aca="false">C41-D41</f>
@@ -20740,12 +20749,12 @@
         <v>194</v>
       </c>
       <c r="C42" s="57" t="n">
-        <f aca="false">GERMANY!E30</f>
-        <v>2993651.0798</v>
+        <f aca="false">IF(OR(Dashboard!H15&lt;=Inputs!$B$38+0.0000001,Dashboard!F15=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D42" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I16,'Dashboard (2)'!Z23)</f>
-        <v>2993651.0798</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E42" s="57" t="n">
         <f aca="false">C42-D42</f>
@@ -20764,7 +20773,7 @@
         <v>195</v>
       </c>
       <c r="C43" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H16&lt;=Inputs!$B$38+0.0000001,Dashboard!F16=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM19&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM19='Dashboard (2)'!Y19),1,0)</f>
         <v>1</v>
       </c>
       <c r="D43" s="57" t="n">
@@ -20788,12 +20797,12 @@
         <v>196</v>
       </c>
       <c r="C44" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM23&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM23='Dashboard (2)'!Y23),1,0)</f>
-        <v>1</v>
+        <f aca="false">GERMANY!E30</f>
+        <v>2993651.0798</v>
       </c>
       <c r="D44" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I16,'Dashboard (2)'!Z23)</f>
+        <v>2993651.0798</v>
       </c>
       <c r="E44" s="57" t="n">
         <f aca="false">C44-D44</f>
@@ -20812,12 +20821,12 @@
         <v>197</v>
       </c>
       <c r="C45" s="57" t="n">
-        <f aca="false">BELGIUM!E30</f>
-        <v>2345890.3695</v>
+        <f aca="false">IF(OR(Dashboard!H16&lt;=Inputs!$B$38+0.0000001,Dashboard!F16=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D45" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I17,'Dashboard (2)'!Z26)</f>
-        <v>2345890.3695</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E45" s="57" t="n">
         <f aca="false">C45-D45</f>
@@ -20836,7 +20845,7 @@
         <v>198</v>
       </c>
       <c r="C46" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H17&lt;=Inputs!$B$38+0.0000001,Dashboard!F17=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM23&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM23='Dashboard (2)'!Y23),1,0)</f>
         <v>1</v>
       </c>
       <c r="D46" s="57" t="n">
@@ -20860,12 +20869,12 @@
         <v>199</v>
       </c>
       <c r="C47" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM26&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM26='Dashboard (2)'!Y26),1,0)</f>
-        <v>1</v>
+        <f aca="false">BELGIUM!E30</f>
+        <v>2345890.3695</v>
       </c>
       <c r="D47" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I17,'Dashboard (2)'!Z26)</f>
+        <v>2345890.3695</v>
       </c>
       <c r="E47" s="57" t="n">
         <f aca="false">C47-D47</f>
@@ -20884,12 +20893,12 @@
         <v>200</v>
       </c>
       <c r="C48" s="57" t="n">
-        <f aca="false">PORTUGAL!E30</f>
-        <v>1926457.8217</v>
+        <f aca="false">IF(OR(Dashboard!H17&lt;=Inputs!$B$38+0.0000001,Dashboard!F17=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D48" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I18,'Dashboard (2)'!Z30)</f>
-        <v>1926457.8217</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E48" s="57" t="n">
         <f aca="false">C48-D48</f>
@@ -20908,7 +20917,7 @@
         <v>201</v>
       </c>
       <c r="C49" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H18&lt;=Inputs!$B$38+0.0000001,Dashboard!F18=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM26&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM26='Dashboard (2)'!Y26),1,0)</f>
         <v>1</v>
       </c>
       <c r="D49" s="57" t="n">
@@ -20932,12 +20941,12 @@
         <v>202</v>
       </c>
       <c r="C50" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM30&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM30='Dashboard (2)'!Y30),1,0)</f>
-        <v>1</v>
+        <f aca="false">PORTUGAL!E30</f>
+        <v>1926457.8217</v>
       </c>
       <c r="D50" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I18,'Dashboard (2)'!Z30)</f>
+        <v>1926457.8217</v>
       </c>
       <c r="E50" s="57" t="n">
         <f aca="false">C50-D50</f>
@@ -20956,12 +20965,12 @@
         <v>203</v>
       </c>
       <c r="C51" s="57" t="n">
-        <f aca="false">IRELAND!E30</f>
-        <v>1290623.255</v>
+        <f aca="false">IF(OR(Dashboard!H18&lt;=Inputs!$B$38+0.0000001,Dashboard!F18=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D51" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I19,'Dashboard (2)'!Z34)</f>
-        <v>1290623.255</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E51" s="57" t="n">
         <f aca="false">C51-D51</f>
@@ -20980,7 +20989,7 @@
         <v>204</v>
       </c>
       <c r="C52" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H19&lt;=Inputs!$B$38+0.0000001,Dashboard!F19=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM30&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM30='Dashboard (2)'!Y30),1,0)</f>
         <v>1</v>
       </c>
       <c r="D52" s="57" t="n">
@@ -21004,12 +21013,12 @@
         <v>205</v>
       </c>
       <c r="C53" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM34&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM34='Dashboard (2)'!Y34),1,0)</f>
-        <v>1</v>
+        <f aca="false">IRELAND!E30</f>
+        <v>1290623.255</v>
       </c>
       <c r="D53" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I19,'Dashboard (2)'!Z34)</f>
+        <v>1290623.255</v>
       </c>
       <c r="E53" s="57" t="n">
         <f aca="false">C53-D53</f>
@@ -21028,12 +21037,12 @@
         <v>206</v>
       </c>
       <c r="C54" s="57" t="n">
-        <f aca="false">GREECE!E30</f>
-        <v>595224.3791</v>
+        <f aca="false">IF(OR(Dashboard!H19&lt;=Inputs!$B$38+0.0000001,Dashboard!F19=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D54" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I20,'Dashboard (2)'!Z37)</f>
-        <v>595224.3791</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E54" s="57" t="n">
         <f aca="false">C54-D54</f>
@@ -21052,7 +21061,7 @@
         <v>207</v>
       </c>
       <c r="C55" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H20&lt;=Inputs!$B$38+0.0000001,Dashboard!F20=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM34&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM34='Dashboard (2)'!Y34),1,0)</f>
         <v>1</v>
       </c>
       <c r="D55" s="57" t="n">
@@ -21076,12 +21085,12 @@
         <v>208</v>
       </c>
       <c r="C56" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM37&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM37='Dashboard (2)'!Y37),1,0)</f>
-        <v>1</v>
+        <f aca="false">GREECE!E30</f>
+        <v>595224.3791</v>
       </c>
       <c r="D56" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I20,'Dashboard (2)'!Z37)</f>
+        <v>595224.3791</v>
       </c>
       <c r="E56" s="57" t="n">
         <f aca="false">C56-D56</f>
@@ -21100,12 +21109,12 @@
         <v>209</v>
       </c>
       <c r="C57" s="57" t="n">
-        <f aca="false">CYPRUS!E30</f>
-        <v>554203.8032</v>
+        <f aca="false">IF(OR(Dashboard!H20&lt;=Inputs!$B$38+0.0000001,Dashboard!F20=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D57" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I21,'Dashboard (2)'!Z40)</f>
-        <v>554203.8032</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E57" s="57" t="n">
         <f aca="false">C57-D57</f>
@@ -21124,7 +21133,7 @@
         <v>210</v>
       </c>
       <c r="C58" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H21&lt;=Inputs!$B$38+0.0000001,Dashboard!F21=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM37&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM37='Dashboard (2)'!Y37),1,0)</f>
         <v>1</v>
       </c>
       <c r="D58" s="57" t="n">
@@ -21148,12 +21157,12 @@
         <v>211</v>
       </c>
       <c r="C59" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM40&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM40='Dashboard (2)'!Y40),1,0)</f>
-        <v>1</v>
+        <f aca="false">CYPRUS!E30</f>
+        <v>554203.8032</v>
       </c>
       <c r="D59" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I21,'Dashboard (2)'!Z40)</f>
+        <v>554203.8032</v>
       </c>
       <c r="E59" s="57" t="n">
         <f aca="false">C59-D59</f>
@@ -21172,12 +21181,12 @@
         <v>212</v>
       </c>
       <c r="C60" s="57" t="n">
-        <f aca="false">MALTA!E30</f>
-        <v>240738.246</v>
+        <f aca="false">IF(OR(Dashboard!H21&lt;=Inputs!$B$38+0.0000001,Dashboard!F21=0),1,0)</f>
+        <v>1</v>
       </c>
       <c r="D60" s="57" t="n">
-        <f aca="false">AVERAGE(Dashboard!I22,'Dashboard (2)'!Z43)</f>
-        <v>240738.246</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="E60" s="57" t="n">
         <f aca="false">C60-D60</f>
@@ -21196,7 +21205,7 @@
         <v>213</v>
       </c>
       <c r="C61" s="57" t="n">
-        <f aca="false">IF(OR(Dashboard!H22&lt;=Inputs!$B$38+0.0000001,Dashboard!F22=0),1,0)</f>
+        <f aca="false">IF(OR('Dashboard (2)'!BM40&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM40='Dashboard (2)'!Y40),1,0)</f>
         <v>1</v>
       </c>
       <c r="D61" s="57" t="n">
@@ -21220,12 +21229,12 @@
         <v>214</v>
       </c>
       <c r="C62" s="57" t="n">
-        <f aca="false">IF(OR('Dashboard (2)'!BM43&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM43='Dashboard (2)'!Y43),1,0)</f>
-        <v>1</v>
+        <f aca="false">MALTA!E30</f>
+        <v>240738.246</v>
       </c>
       <c r="D62" s="57" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
+        <f aca="false">AVERAGE(Dashboard!I22,'Dashboard (2)'!Z43)</f>
+        <v>240738.246</v>
       </c>
       <c r="E62" s="57" t="n">
         <f aca="false">C62-D62</f>
@@ -21237,28 +21246,76 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="C63" s="57" t="n">
+        <f aca="false">IF(OR(Dashboard!H22&lt;=Inputs!$B$38+0.0000001,Dashboard!F22=0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D63" s="57" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="E63" s="57" t="n">
+        <f aca="false">C63-D63</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="0" t="str">
+        <f aca="false">IF(ABS(E63)&lt;1,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C64" s="57" t="n">
+        <f aca="false">IF(OR('Dashboard (2)'!BM43&lt;=Inputs!$B$38+0.0000001,'Dashboard (2)'!BM43='Dashboard (2)'!Y43),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D64" s="57" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="E64" s="57" t="n">
+        <f aca="false">C64-D64</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="0" t="str">
+        <f aca="false">IF(ABS(E64)&lt;1,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="0" t="n">
         <f aca="false">COUNTIF(Dashboard!H7:H22,"&gt;1")</f>
         <v>2</v>
       </c>
-      <c r="F63" s="0" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="6" t="s">
+      <c r="F65" s="0" t="s">
         <v>219</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -21307,12 +21364,12 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="68" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B3" s="68"/>
       <c r="C3" s="68"/>
@@ -21326,12 +21383,12 @@
       <c r="K3" s="69"/>
       <c r="L3" s="69"/>
       <c r="M3" s="70" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N3" s="70"/>
       <c r="O3" s="69"/>
       <c r="P3" s="71" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q3" s="71"/>
       <c r="R3" s="71"/>
@@ -21375,35 +21432,35 @@
       <c r="K4" s="69"/>
       <c r="L4" s="69"/>
       <c r="M4" s="73" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N4" s="74" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O4" s="69"/>
       <c r="P4" s="75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q4" s="76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R4" s="76" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="S4" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="T4" s="76" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="U4" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="V4" s="76" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="W4" s="76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21417,11 +21474,12 @@
         <v>6974170.0524</v>
       </c>
       <c r="D5" s="61" t="n">
-        <v>13051952.5629</v>
+        <f aca="false">'Dashboard (2)'!X9</f>
+        <v>12535797.12</v>
       </c>
       <c r="E5" s="56" t="n">
         <f aca="false">C5/D5</f>
-        <v>0.534339212373786</v>
+        <v>0.556340373542995</v>
       </c>
       <c r="G5" s="78" t="n">
         <v>376073.9136</v>
@@ -21431,7 +21489,7 @@
         <v>7350243.966</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="K5" s="81"/>
       <c r="L5" s="82" t="n">
@@ -21446,7 +21504,7 @@
       </c>
       <c r="O5" s="81"/>
       <c r="P5" s="85" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q5" s="81"/>
       <c r="R5" s="81"/>
@@ -21454,7 +21512,7 @@
       <c r="T5" s="81"/>
       <c r="V5" s="86"/>
       <c r="W5" s="87" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21468,11 +21526,12 @@
         <v>3098113.5036</v>
       </c>
       <c r="D6" s="61" t="n">
-        <v>8834692</v>
+        <f aca="false">'Dashboard (2)'!X10</f>
+        <v>8485128.96</v>
       </c>
       <c r="E6" s="56" t="n">
         <f aca="false">C6/D6</f>
-        <v>0.350675892674017</v>
+        <v>0.365122736284258</v>
       </c>
       <c r="G6" s="78" t="n">
         <v>159024.456</v>
@@ -21482,7 +21541,7 @@
         <v>3257137.9596</v>
       </c>
       <c r="J6" s="80" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="K6" s="81"/>
       <c r="L6" s="82" t="n">
@@ -21493,7 +21552,7 @@
       <c r="N6" s="81"/>
       <c r="O6" s="81"/>
       <c r="P6" s="85" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q6" s="81"/>
       <c r="R6" s="81"/>
@@ -21501,7 +21560,7 @@
       <c r="T6" s="81"/>
       <c r="V6" s="86"/>
       <c r="W6" s="87" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21570,10 +21629,10 @@
         <v>22981703</v>
       </c>
       <c r="V7" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W7" s="87" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21624,7 +21683,7 @@
       </c>
       <c r="O8" s="81"/>
       <c r="P8" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q8" s="81"/>
       <c r="R8" s="81"/>
@@ -21635,10 +21694,10 @@
         <v>0.018</v>
       </c>
       <c r="V8" s="94" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="W8" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21707,10 +21766,10 @@
         <v>5640960</v>
       </c>
       <c r="V9" s="86" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="W9" s="87" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21779,10 +21838,10 @@
         <v>3533131</v>
       </c>
       <c r="V10" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W10" s="87" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21833,7 +21892,7 @@
       </c>
       <c r="O11" s="81"/>
       <c r="P11" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
@@ -21844,10 +21903,10 @@
         <v>0.018</v>
       </c>
       <c r="V11" s="94" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="W11" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21886,7 +21945,7 @@
         <v>366480.3</v>
       </c>
       <c r="J12" s="55" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K12" s="81"/>
       <c r="L12" s="82" t="n">
@@ -21901,7 +21960,7 @@
       </c>
       <c r="O12" s="81"/>
       <c r="P12" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q12" s="81"/>
       <c r="R12" s="81"/>
@@ -21912,10 +21971,10 @@
         <v>0.018</v>
       </c>
       <c r="V12" s="94" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="W12" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21984,10 +22043,10 @@
         <v>458894</v>
       </c>
       <c r="V13" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W13" s="87" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22056,10 +22115,10 @@
         <v>671653</v>
       </c>
       <c r="V14" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W14" s="87" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22128,10 +22187,10 @@
         <v>217083</v>
       </c>
       <c r="V15" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W15" s="87" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22182,7 +22241,7 @@
       </c>
       <c r="O16" s="81"/>
       <c r="P16" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q16" s="81"/>
       <c r="R16" s="81"/>
@@ -22193,10 +22252,10 @@
         <v>0.018</v>
       </c>
       <c r="V16" s="94" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="W16" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22235,7 +22294,7 @@
         <v>2345890.3695</v>
       </c>
       <c r="J17" s="55" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K17" s="81"/>
       <c r="L17" s="82" t="n">
@@ -22268,10 +22327,10 @@
         <v>7621476</v>
       </c>
       <c r="V17" s="86" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="W17" s="87" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22340,10 +22399,10 @@
         <v>4933599</v>
       </c>
       <c r="V18" s="86" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="W18" s="87" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22382,7 +22441,7 @@
         <v>1290623.255</v>
       </c>
       <c r="J19" s="55" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K19" s="81"/>
       <c r="L19" s="82" t="n">
@@ -22415,10 +22474,10 @@
         <v>3752695</v>
       </c>
       <c r="V19" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W19" s="87" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22469,7 +22528,7 @@
       </c>
       <c r="O20" s="81"/>
       <c r="P20" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q20" s="81"/>
       <c r="R20" s="81"/>
@@ -22480,10 +22539,10 @@
         <v>0.018</v>
       </c>
       <c r="V20" s="94" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="W20" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22530,7 +22589,7 @@
       <c r="N21" s="81"/>
       <c r="O21" s="81"/>
       <c r="P21" s="93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q21" s="81"/>
       <c r="R21" s="81"/>
@@ -22541,10 +22600,10 @@
         <v>0.018</v>
       </c>
       <c r="V21" s="94" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W21" s="95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22613,10 +22672,10 @@
         <v>610918</v>
       </c>
       <c r="V22" s="86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="W22" s="87" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22629,11 +22688,11 @@
       </c>
       <c r="D23" s="79" t="n">
         <f aca="false">SUM(D5:D22)</f>
-        <v>61019133.4129</v>
+        <v>60153414.93</v>
       </c>
       <c r="E23" s="96" t="n">
         <f aca="false">C23/D23</f>
-        <v>0.544458108429585</v>
+        <v>0.552293863858944</v>
       </c>
       <c r="G23" s="79" t="n">
         <f aca="false">SUM(G5:G22)</f>
@@ -22710,7 +22769,7 @@
     </row>
     <row r="30" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="80" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22792,7 +22851,7 @@
         <v>-287445.7464427</v>
       </c>
       <c r="T4" s="100" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22800,10 +22859,10 @@
         <v>210000</v>
       </c>
       <c r="P5" s="101" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q5" s="102" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="R5" s="99" t="n">
         <v>-260000</v>
@@ -22815,7 +22874,7 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="O6" s="101" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R6" s="104"/>
       <c r="S6" s="99" t="n">
@@ -22828,7 +22887,7 @@
         <v>378908</v>
       </c>
       <c r="R7" s="105" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="S7" s="104"/>
       <c r="T7" s="99" t="n">
@@ -22840,10 +22899,10 @@
         <v>93000</v>
       </c>
       <c r="N8" s="101" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="S8" s="106" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="T8" s="107"/>
     </row>
@@ -22854,7 +22913,7 @@
       <c r="N9" s="101"/>
       <c r="T9" s="107"/>
       <c r="U9" s="101" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="V9" s="99" t="n">
         <f aca="false">-Q4</f>
@@ -22866,18 +22925,18 @@
         <v>280000</v>
       </c>
       <c r="K10" s="101" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L10" s="101"/>
       <c r="M10" s="101" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N10" s="108" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="T10" s="107"/>
       <c r="U10" s="67" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22888,13 +22947,13 @@
         <v>11940</v>
       </c>
       <c r="J11" s="101" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M11" s="109" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N11" s="110" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="T11" s="107"/>
     </row>
@@ -22903,17 +22962,17 @@
         <v>75000</v>
       </c>
       <c r="H12" s="101" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I12" s="101" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N12" s="110" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="T12" s="107"/>
       <c r="U12" s="101" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22921,20 +22980,20 @@
         <v>60000</v>
       </c>
       <c r="G13" s="101" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H13" s="110" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I13" s="110" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N13" s="110" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="T13" s="107"/>
       <c r="U13" s="110" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="V13" s="99" t="n">
         <v>376073.9136</v>
@@ -22945,20 +23004,20 @@
         <v>96664.1975427</v>
       </c>
       <c r="F14" s="101" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H14" s="110" t="s">
+        <v>290</v>
+      </c>
+      <c r="I14" s="110" t="s">
+        <v>291</v>
+      </c>
+      <c r="N14" s="110" t="s">
         <v>287</v>
-      </c>
-      <c r="I14" s="110" t="s">
-        <v>288</v>
-      </c>
-      <c r="N14" s="110" t="s">
-        <v>284</v>
       </c>
       <c r="T14" s="107"/>
       <c r="U14" s="110" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="V14" s="99" t="n">
         <v>159024.456</v>
@@ -22969,17 +23028,17 @@
         <v>691851.847800002</v>
       </c>
       <c r="E15" s="101" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H15" s="110" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I15" s="110" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="T15" s="107"/>
       <c r="U15" s="110" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V15" s="99" t="n">
         <f aca="false">IUK!E23</f>
@@ -22991,17 +23050,17 @@
         <v>32944042.77</v>
       </c>
       <c r="D16" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="H16" s="110" t="s">
+        <v>295</v>
+      </c>
+      <c r="I16" s="110" t="s">
         <v>294</v>
-      </c>
-      <c r="H16" s="110" t="s">
-        <v>292</v>
-      </c>
-      <c r="I16" s="110" t="s">
-        <v>291</v>
       </c>
       <c r="T16" s="107"/>
       <c r="U16" s="110" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="V16" s="99" t="n">
         <f aca="false">UMI!E23</f>
@@ -23011,14 +23070,14 @@
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="111"/>
       <c r="H17" s="110" t="s">
+        <v>299</v>
+      </c>
+      <c r="I17" s="110" t="s">
         <v>296</v>
-      </c>
-      <c r="I17" s="110" t="s">
-        <v>293</v>
       </c>
       <c r="T17" s="112"/>
       <c r="U17" s="110" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="V17" s="99" t="n">
         <f aca="false">NORWAY!E23</f>
@@ -23028,14 +23087,14 @@
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="111"/>
       <c r="H18" s="110" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I18" s="110" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="T18" s="112"/>
       <c r="U18" s="110" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="V18" s="99" t="n">
         <f aca="false">SWEDEN!E23</f>
@@ -23045,14 +23104,14 @@
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="111"/>
       <c r="H19" s="110" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I19" s="110" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="T19" s="112"/>
       <c r="U19" s="110" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="V19" s="99" t="n">
         <f aca="false">HUNGARY!E23</f>
@@ -23063,7 +23122,7 @@
       <c r="C20" s="111"/>
       <c r="T20" s="112"/>
       <c r="U20" s="110" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="V20" s="99" t="n">
         <f aca="false">FINLAND!E23</f>
@@ -23074,7 +23133,7 @@
       <c r="C21" s="111"/>
       <c r="T21" s="112"/>
       <c r="U21" s="110" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="V21" s="99" t="n">
         <f aca="false">ROMANIA!E23</f>
@@ -23085,7 +23144,7 @@
       <c r="C22" s="111"/>
       <c r="T22" s="112"/>
       <c r="U22" s="110" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="V22" s="99" t="n">
         <f aca="false">DENMARK!E23</f>
@@ -23096,7 +23155,7 @@
       <c r="C23" s="111"/>
       <c r="T23" s="112"/>
       <c r="U23" s="110" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="V23" s="99" t="n">
         <f aca="false">ICELAND!E23</f>
@@ -23107,7 +23166,7 @@
       <c r="C24" s="111"/>
       <c r="T24" s="112"/>
       <c r="U24" s="110" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="V24" s="99" t="n">
         <f aca="false">GERMANY!E29</f>
@@ -23116,13 +23175,13 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="113" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="T25" s="114" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="U25" s="110" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="V25" s="99" t="n">
         <f aca="false">BELGIUM!E29</f>
@@ -23131,7 +23190,7 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U26" s="110" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="V26" s="99" t="n">
         <f aca="false">PORTUGAL!E29</f>
@@ -23140,7 +23199,7 @@
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U27" s="110" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="V27" s="99" t="n">
         <f aca="false">IRELAND!E29</f>
@@ -23149,7 +23208,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U28" s="110" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="V28" s="99" t="n">
         <f aca="false">GREECE!E29</f>
@@ -23158,7 +23217,7 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U29" s="110" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="V29" s="99" t="n">
         <f aca="false">CYPRUS!E29</f>
@@ -23167,7 +23226,7 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U30" s="110" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="V30" s="99" t="n">
         <f aca="false">MALTA!E29</f>
@@ -23176,7 +23235,7 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="U31" s="101" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="V31" s="99" t="n">
         <f aca="false">SUM(V13:V30)</f>
@@ -23210,32 +23269,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -23243,30 +23302,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23297,7 +23356,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -23330,39 +23389,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -23396,40 +23455,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -23462,7 +23521,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>7297065.71</v>
@@ -23477,7 +23536,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -23494,7 +23553,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -23509,7 +23568,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -23526,7 +23585,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -23543,7 +23602,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -23560,33 +23619,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>18843292.94</v>
@@ -23595,12 +23654,12 @@
         <v>21418279</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -23610,7 +23669,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -23619,7 +23678,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -23628,17 +23687,17 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -23668,32 +23727,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -23701,30 +23760,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23755,7 +23814,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -23788,39 +23847,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -23854,40 +23913,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -23920,7 +23979,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>2739215.7</v>
@@ -23935,7 +23994,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -23952,7 +24011,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -23967,7 +24026,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -23984,7 +24043,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -24001,7 +24060,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -24018,43 +24077,43 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123"/>
       <c r="D30" s="123"/>
       <c r="F30" s="131" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -24064,7 +24123,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -24073,7 +24132,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="str">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -24082,22 +24141,22 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="80" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -24127,32 +24186,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -24160,30 +24219,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24214,7 +24273,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -24247,39 +24306,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -24313,40 +24372,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -24379,7 +24438,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>1162750.67</v>
@@ -24394,7 +24453,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -24411,7 +24470,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -24426,7 +24485,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -24443,7 +24502,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -24460,7 +24519,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -24477,33 +24536,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>3367988</v>
@@ -24512,12 +24571,12 @@
         <v>4811395</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -24527,7 +24586,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -24536,7 +24595,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -24545,22 +24604,22 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="80" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -24590,32 +24649,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F3" s="77" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F4" s="115" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I6" s="67" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" s="117" t="n">
         <v>1.16</v>
@@ -24623,30 +24682,30 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G8" s="72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H8" s="72" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I8" s="72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24677,7 +24736,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C10" s="61" t="n">
         <f aca="false">C9</f>
@@ -24710,39 +24769,39 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" s="119"/>
       <c r="D13" s="119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F13" s="119" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="119" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="119" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I13" s="119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="120" t="n">
         <f aca="false">Inputs!$B$4</f>
@@ -24776,40 +24835,40 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="98" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H18" s="72" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I18" s="72" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C19" s="61" t="n">
         <f aca="false">C9*$D$14</f>
@@ -24842,7 +24901,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C20" s="123" t="n">
         <v>1215958.33</v>
@@ -24857,7 +24916,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="96" t="n">
         <f aca="false">C20/C19</f>
@@ -24874,7 +24933,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" s="124" t="n">
         <v>0</v>
@@ -24889,7 +24948,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">C19*C22</f>
@@ -24906,7 +24965,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C24" s="79" t="n">
         <f aca="false">C20+C23</f>
@@ -24923,7 +24982,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="56" t="n">
         <f aca="false">C24/C19</f>
@@ -24940,33 +24999,33 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="125" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C30" s="123" t="n">
         <v>2482560</v>
@@ -24975,12 +25034,12 @@
         <v>3154221.508</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B31" s="126" t="n">
         <v>0.35</v>
@@ -24990,7 +25049,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="128" t="n">
         <f aca="false">-E23/(B31-1)</f>
@@ -24999,7 +25058,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E33" s="129" t="n">
         <f aca="false">IF(OR(D30="",D30="no KPI data"),"no KPI data",D30+E32)</f>
@@ -25008,17 +25067,17 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="130" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
